--- a/documentation/DataFabricSchema.xlsx
+++ b/documentation/DataFabricSchema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/josephrumpza/projects/provider-onboarding-demo/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EAB275-4FEA-744F-B23F-9E0A1FB37941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D08D8A-1808-6C4C-A212-495E2FBB37A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25700" yWindow="-24400" windowWidth="24900" windowHeight="16760" xr2:uid="{163A9318-C749-C547-A71F-27E911A0EC98}"/>
+    <workbookView xWindow="40880" yWindow="3980" windowWidth="35760" windowHeight="26080" xr2:uid="{163A9318-C749-C547-A71F-27E911A0EC98}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="91">
   <si>
     <t>StorageBucketPath</t>
   </si>
@@ -59,12 +59,6 @@
     <t>Storage Bucket Path</t>
   </si>
   <si>
-    <t>Received At</t>
-  </si>
-  <si>
-    <t>ReceivedAt</t>
-  </si>
-  <si>
     <t>Document Type</t>
   </si>
   <si>
@@ -116,12 +110,6 @@
     <t>ActivityCategory</t>
   </si>
   <si>
-    <t>Activity Details</t>
-  </si>
-  <si>
-    <t>ActivityDetails</t>
-  </si>
-  <si>
     <t>Activity Description</t>
   </si>
   <si>
@@ -228,6 +216,102 @@
   </si>
   <si>
     <t>Provider Onboarding Main Record</t>
+  </si>
+  <si>
+    <t>Case Reference ID</t>
+  </si>
+  <si>
+    <t>Received_CV</t>
+  </si>
+  <si>
+    <t>Received_I9</t>
+  </si>
+  <si>
+    <t>Received_Screening</t>
+  </si>
+  <si>
+    <t>Received_ID</t>
+  </si>
+  <si>
+    <t>Received_EID</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Received_License</t>
+  </si>
+  <si>
+    <t>Received_CredentialList</t>
+  </si>
+  <si>
+    <t>Received_NewHireList</t>
+  </si>
+  <si>
+    <t>Candidate NPI</t>
+  </si>
+  <si>
+    <t>Received_NHP</t>
+  </si>
+  <si>
+    <t>Candidate Email</t>
+  </si>
+  <si>
+    <t>Completed_Physical</t>
+  </si>
+  <si>
+    <t>Completed_Preboarding</t>
+  </si>
+  <si>
+    <t>Received_Headshot</t>
+  </si>
+  <si>
+    <t>Completed_BackgroundCheck</t>
+  </si>
+  <si>
+    <t>Completed_HRISPrep</t>
+  </si>
+  <si>
+    <t>PCN</t>
+  </si>
+  <si>
+    <t>Updated when doc received from new hire</t>
+  </si>
+  <si>
+    <t>Updated based on other events occuring</t>
+  </si>
+  <si>
+    <t>Updated when message received from internal team</t>
+  </si>
+  <si>
+    <t>Generated at start</t>
+  </si>
+  <si>
+    <t>Known at start</t>
+  </si>
+  <si>
+    <t>Updated once during process</t>
+  </si>
+  <si>
+    <t>Updated at start of process and maybe later</t>
+  </si>
+  <si>
+    <t>Updated multiple times</t>
+  </si>
+  <si>
+    <t>Initial Preboarding, HRIS Setup, Clearance and Credentialing, Final Preboarding, Onboarding, Complete</t>
+  </si>
+  <si>
+    <t>Activity Name</t>
+  </si>
+  <si>
+    <t>ActivityName</t>
+  </si>
+  <si>
+    <t>Received Dare</t>
+  </si>
+  <si>
+    <t>ReceivedDate</t>
   </si>
 </sst>
 </file>
@@ -277,12 +361,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -297,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -306,6 +414,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,28 +758,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5966FCCE-B58D-F745-989C-083B6E24E6CC}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="5"/>
       <c r="D1" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E1" s="5"/>
       <c r="G1" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H1" s="5"/>
     </row>
@@ -694,17 +812,17 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.2">
@@ -715,220 +833,447 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10" s="4"/>
       <c r="G10" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" s="4"/>
       <c r="G11" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="D12" s="4"/>
       <c r="G12" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="G13" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="G14" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="G15" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="G16" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="7:8" ht="18" x14ac:dyDescent="0.2">
       <c r="G17" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="7:8" ht="18" x14ac:dyDescent="0.2">
       <c r="G18" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="7:8" ht="18" x14ac:dyDescent="0.2">
       <c r="G19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G26" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G27" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="10"/>
+    </row>
+    <row r="28" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G28" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G29" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G30" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G31" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="10"/>
+    </row>
+    <row r="32" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G32" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32" s="10"/>
+    </row>
+    <row r="33" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G33" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G39" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="7:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G40" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G41" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G42" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G43" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H43" s="8"/>
+    </row>
+    <row r="44" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G44" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G45" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G46" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="7:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="G47" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="7:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G48" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G49" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G51" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H51" s="8"/>
+    </row>
+    <row r="52" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G52" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H52" s="8"/>
+    </row>
+    <row r="53" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="G53" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H53" s="8"/>
+    </row>
+    <row r="54" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="7:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="H58" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G26:G48">
+    <sortCondition ref="G26:G48"/>
+  </sortState>
+  <mergeCells count="7">
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="H39:H46"/>
+    <mergeCell ref="H47:H49"/>
+    <mergeCell ref="H26:H32"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
